--- a/data/trans_camb/IP19C02-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C02-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 5,33</t>
+          <t>-8,21; 4,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 19,69</t>
+          <t>1,31; 18,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,08; 34,01</t>
+          <t>13,96; 34,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 7,26</t>
+          <t>-4,98; 6,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,33; 27,26</t>
+          <t>8,67; 27,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,82; 35,89</t>
+          <t>10,27; 34,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 3,91</t>
+          <t>-4,62; 3,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,74; 20,5</t>
+          <t>8,49; 21,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,18; 32,35</t>
+          <t>15,95; 31,37</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-81,55; 194,17</t>
+          <t>-81,49; 161,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,14; 624,39</t>
+          <t>6,43; 528,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>115,44; 1101,13</t>
+          <t>109,63; 1039,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-68,23; 446,39</t>
+          <t>-71,43; 503,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>100,14; 1481,09</t>
+          <t>88,76; 1396,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>165,99; 1888,32</t>
+          <t>147,62; 2147,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,41; 120,72</t>
+          <t>-59,73; 129,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91,46; 603,93</t>
+          <t>101,5; 705,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>195,37; 963,84</t>
+          <t>205,08; 956,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 0,62</t>
+          <t>-9,38; 0,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 18,61</t>
+          <t>4,42; 19,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,3; 35,73</t>
+          <t>19,5; 36,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 3,81</t>
+          <t>-6,96; 3,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 19,25</t>
+          <t>4,6; 19,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,21; 42,57</t>
+          <t>26,72; 42,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 0,64</t>
+          <t>-6,34; 0,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 16,96</t>
+          <t>6,4; 16,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,05; 37,54</t>
+          <t>26,11; 38,23</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-81,28; 22,97</t>
+          <t>-83,26; 21,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,6; 337,49</t>
+          <t>33,31; 360,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156,63; 673,65</t>
+          <t>164,31; 670,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,02; 88,15</t>
+          <t>-67,04; 82,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,81; 392,75</t>
+          <t>37,7; 417,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>219,85; 909,61</t>
+          <t>224,11; 881,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,49; 12,13</t>
+          <t>-63,49; 16,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,87; 287,03</t>
+          <t>61,71; 269,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>241,22; 622,23</t>
+          <t>252,81; 660,69</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 6,06</t>
+          <t>-6,85; 5,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,06; 18,38</t>
+          <t>3,41; 19,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,18; 22,78</t>
+          <t>6,12; 22,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 0,92</t>
+          <t>-10,55; 0,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 23,56</t>
+          <t>4,31; 23,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 24,73</t>
+          <t>4,32; 24,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 1,46</t>
+          <t>-6,81; 1,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,34; 18,28</t>
+          <t>6,08; 18,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,58; 20,98</t>
+          <t>7,58; 20,61</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-72,31; 202,12</t>
+          <t>-76,15; 172,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,61; 534,46</t>
+          <t>20,44; 539,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39,31; 634,38</t>
+          <t>48,89; 676,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-93,07; 72,92</t>
+          <t>-93,18; 51,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,72; 610,29</t>
+          <t>26,27; 530,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,66; 602,95</t>
+          <t>31,17; 559,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-73,43; 35,91</t>
+          <t>-71,63; 39,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>66,63; 383,17</t>
+          <t>68,21; 411,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>80,78; 479,83</t>
+          <t>72,97; 457,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 7,32</t>
+          <t>-6,07; 7,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,76; 22,09</t>
+          <t>5,13; 21,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,42; 35,09</t>
+          <t>15,61; 34,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 10,33</t>
+          <t>-3,39; 10,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 17,3</t>
+          <t>2,6; 17,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,92; 31,14</t>
+          <t>13,38; 31,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 7,05</t>
+          <t>-2,9; 7,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,15; 16,82</t>
+          <t>5,41; 16,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,52; 30,29</t>
+          <t>16,7; 29,14</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,69; 151,44</t>
+          <t>-58,07; 160,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>47,55; 542,59</t>
+          <t>41,65; 457,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>138,72; 867,56</t>
+          <t>131,32; 734,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-38,43; 272,5</t>
+          <t>-37,99; 273,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,11; 449,7</t>
+          <t>12,67; 433,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>112,01; 773,86</t>
+          <t>123,98; 829,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,92; 130,62</t>
+          <t>-32,29; 139,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>55,53; 323,46</t>
+          <t>49,66; 320,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>174,54; 588,5</t>
+          <t>161,37; 598,78</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 1,55</t>
+          <t>-4,69; 1,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,55; 15,62</t>
+          <t>7,84; 15,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,6; 26,88</t>
+          <t>17,83; 27,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 2,72</t>
+          <t>-3,35; 2,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,86; 16,75</t>
+          <t>8,77; 17,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,39; 29,93</t>
+          <t>20,17; 30,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,21</t>
+          <t>-3,19; 1,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,25; 14,93</t>
+          <t>9,57; 15,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,52; 27,09</t>
+          <t>20,2; 27,1</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,04; 28,52</t>
+          <t>-50,66; 29,71</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>81,22; 271,1</t>
+          <t>85,75; 277,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195,61; 482,5</t>
+          <t>195,16; 490,86</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 51,73</t>
+          <t>-40,42; 52,99</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>109,15; 321,82</t>
+          <t>105,21; 330,28</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>238,63; 593,22</t>
+          <t>233,43; 562,85</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 20,54</t>
+          <t>-40,26; 18,37</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>112,14; 258,28</t>
+          <t>118,61; 253,58</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>250,88; 465,36</t>
+          <t>242,06; 445,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C02-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C02-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 4,83</t>
+          <t>-7,54; 5,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 18,88</t>
+          <t>1,53; 18,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,96; 34,2</t>
+          <t>13,39; 34,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 6,89</t>
+          <t>-4,67; 7,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,67; 27,55</t>
+          <t>8,71; 27,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,27; 34,99</t>
+          <t>12,18; 35,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 3,8</t>
+          <t>-4,48; 3,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,49; 21,02</t>
+          <t>8,07; 21,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,95; 31,37</t>
+          <t>15,96; 31,39</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-81,49; 161,84</t>
+          <t>-79,71; 224,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 528,81</t>
+          <t>8,56; 590,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109,63; 1039,74</t>
+          <t>115,51; 984,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-71,43; 503,51</t>
+          <t>-72,34; 377,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,76; 1396,47</t>
+          <t>93,37; 1494,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>147,62; 2147,36</t>
+          <t>166,62; 1984,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,73; 129,3</t>
+          <t>-64,44; 123,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>101,5; 705,1</t>
+          <t>92,26; 628,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>205,08; 956,8</t>
+          <t>205,9; 990,36</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 0,93</t>
+          <t>-9,37; 0,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 19,21</t>
+          <t>4,27; 18,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,5; 36,34</t>
+          <t>18,04; 35,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 3,79</t>
+          <t>-6,85; 3,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,6; 19,72</t>
+          <t>4,61; 19,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,72; 42,72</t>
+          <t>27,2; 42,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 0,94</t>
+          <t>-6,4; 0,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 16,64</t>
+          <t>6,69; 17,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,11; 38,23</t>
+          <t>26,34; 38,35</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-83,26; 21,73</t>
+          <t>-80,91; 13,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,31; 360,98</t>
+          <t>33,27; 332,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>164,31; 670,64</t>
+          <t>144,52; 635,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-67,04; 82,91</t>
+          <t>-65,52; 83,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,7; 417,32</t>
+          <t>39,48; 413,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>224,11; 881,88</t>
+          <t>233,6; 893,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,49; 16,53</t>
+          <t>-65,47; 16,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61,71; 269,63</t>
+          <t>63,47; 290,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>252,81; 660,69</t>
+          <t>252,11; 659,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 5,65</t>
+          <t>-6,06; 6,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 19,83</t>
+          <t>2,78; 19,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,12; 22,96</t>
+          <t>5,33; 22,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 0,33</t>
+          <t>-10,26; 0,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,31; 23,2</t>
+          <t>3,78; 22,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 24,17</t>
+          <t>4,14; 23,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 1,31</t>
+          <t>-6,43; 1,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,08; 18,42</t>
+          <t>6,26; 18,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,58; 20,61</t>
+          <t>7,49; 21,04</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-76,15; 172,04</t>
+          <t>-70,05; 202,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,44; 539,72</t>
+          <t>16,63; 590,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48,89; 676,18</t>
+          <t>41,22; 624,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-93,18; 51,09</t>
+          <t>-100,0; 49,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,27; 530,21</t>
+          <t>23,44; 571,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,17; 559,49</t>
+          <t>17,15; 518,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-71,63; 39,22</t>
+          <t>-74,07; 46,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>68,21; 411,29</t>
+          <t>57,27; 389,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72,97; 457,17</t>
+          <t>78,33; 454,85</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 7,36</t>
+          <t>-6,09; 7,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,13; 21,43</t>
+          <t>5,27; 20,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,61; 34,45</t>
+          <t>15,7; 33,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 10,34</t>
+          <t>-3,36; 10,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 17,71</t>
+          <t>2,72; 17,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,38; 31,41</t>
+          <t>14,26; 31,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 7,22</t>
+          <t>-2,7; 6,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 16,69</t>
+          <t>6,01; 17,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,7; 29,14</t>
+          <t>17,01; 29,88</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-58,07; 160,75</t>
+          <t>-59,37; 183,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>41,65; 457,07</t>
+          <t>37,35; 474,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>131,32; 734,09</t>
+          <t>126,7; 706,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,99; 273,99</t>
+          <t>-39,55; 267,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,67; 433,08</t>
+          <t>19,64; 470,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>123,98; 829,97</t>
+          <t>129,12; 892,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,29; 139,71</t>
+          <t>-29,62; 131,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>49,66; 320,78</t>
+          <t>60,42; 333,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>161,37; 598,78</t>
+          <t>170,58; 614,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 1,65</t>
+          <t>-4,59; 1,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,84; 15,89</t>
+          <t>7,72; 15,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,83; 27,53</t>
+          <t>17,62; 26,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 2,74</t>
+          <t>-3,47; 2,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,77; 17,06</t>
+          <t>9,09; 17,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,17; 30,08</t>
+          <t>20,09; 29,84</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 1,14</t>
+          <t>-3,03; 1,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,57; 15,22</t>
+          <t>9,73; 15,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,2; 27,1</t>
+          <t>20,52; 27,43</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,66; 29,71</t>
+          <t>-52,23; 22,77</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>85,75; 277,32</t>
+          <t>79,23; 258,15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195,16; 490,86</t>
+          <t>191,82; 456,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-40,42; 52,99</t>
+          <t>-41,29; 49,25</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>105,21; 330,28</t>
+          <t>109,37; 330,73</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>233,43; 562,85</t>
+          <t>235,84; 601,88</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 18,37</t>
+          <t>-37,67; 17,56</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>118,61; 253,58</t>
+          <t>115,9; 257,19</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>242,06; 445,98</t>
+          <t>253,06; 470,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C02-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C02-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,94</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17,65</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27,27</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-1,38</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>10,11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23,87</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,65</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,27</t>
+          <t>25,39</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24,03</t>
+          <t>26,37</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 5,07</t>
+          <t>-4,26; 7,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 18,44</t>
+          <t>9,33; 27,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,39; 34,22</t>
+          <t>15,66; 39,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 7,31</t>
+          <t>-7,34; 5,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,71; 27,88</t>
+          <t>1,9; 19,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,18; 35,48</t>
+          <t>14,63; 36,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 3,89</t>
+          <t>-4,44; 3,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,07; 21,04</t>
+          <t>7,74; 20,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,96; 31,39</t>
+          <t>18,22; 34,76</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21,79%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>408,54%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>631,2%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-21,39%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>156,88%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>370,48%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>21,79%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>408,54%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>561,59%</t>
+          <t>394,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>450,07%</t>
+          <t>494,02%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-79,71; 224,09</t>
+          <t>-68,23; 446,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,56; 590,21</t>
+          <t>100,14; 1481,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>115,51; 984,34</t>
+          <t>193,06; 2102,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-72,34; 377,02</t>
+          <t>-81,55; 194,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>93,37; 1494,06</t>
+          <t>13,14; 624,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>166,62; 1984,11</t>
+          <t>123,89; 1163,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,44; 123,07</t>
+          <t>-62,41; 120,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>92,26; 628,75</t>
+          <t>91,46; 603,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>205,9; 990,36</t>
+          <t>222,12; 1032,15</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,52</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,77</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36,74</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-4,15</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>11,75</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>27,45</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,52</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,77</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,76</t>
+          <t>29,72</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>31,77</t>
+          <t>33,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 0,46</t>
+          <t>-7,11; 3,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 18,27</t>
+          <t>3,92; 19,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,04; 35,55</t>
+          <t>28,5; 44,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 3,91</t>
+          <t>-9,45; 0,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 19,33</t>
+          <t>4,01; 18,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,2; 42,6</t>
+          <t>20,46; 38,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 0,89</t>
+          <t>-6,58; 0,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 17,17</t>
+          <t>6,57; 16,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,34; 38,35</t>
+          <t>27,85; 39,87</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-19,44%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>150,27%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>468,95%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-50,74%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>143,56%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>335,29%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-19,44%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>150,27%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>443,65%</t>
+          <t>363,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>396,65%</t>
+          <t>421,67%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-80,91; 13,2</t>
+          <t>-65,02; 88,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,27; 332,69</t>
+          <t>25,81; 392,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144,52; 635,3</t>
+          <t>236,6; 953,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,52; 83,57</t>
+          <t>-81,28; 22,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,48; 413,0</t>
+          <t>29,6; 337,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>233,6; 893,57</t>
+          <t>176,84; 726,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,47; 16,21</t>
+          <t>-66,49; 12,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63,47; 290,42</t>
+          <t>65,87; 287,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>252,11; 659,37</t>
+          <t>255,5; 654,2</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-4,49</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13,85</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15,17</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>10,85</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13,64</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,49</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,85</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,38</t>
+          <t>13,8</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13,5</t>
+          <t>14,51</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 6,24</t>
+          <t>-10,14; 0,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 19,14</t>
+          <t>4,19; 23,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,33; 22,82</t>
+          <t>5,57; 27,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 0,64</t>
+          <t>-6,32; 6,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 22,51</t>
+          <t>3,06; 18,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 23,65</t>
+          <t>5,77; 21,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 1,89</t>
+          <t>-6,82; 1,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,26; 18,49</t>
+          <t>6,34; 18,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,49; 21,04</t>
+          <t>8,62; 21,48</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-62,1%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>191,7%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>210,01%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-6,58%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>169,92%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>213,62%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-62,1%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>191,7%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>185,25%</t>
+          <t>216,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>197,73%</t>
+          <t>212,46%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-70,05; 202,99</t>
+          <t>-93,07; 72,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,63; 590,66</t>
+          <t>29,72; 610,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41,22; 624,27</t>
+          <t>36,54; 653,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 49,59</t>
+          <t>-72,31; 202,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,44; 571,74</t>
+          <t>23,61; 534,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,15; 518,54</t>
+          <t>47,38; 616,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-74,07; 46,87</t>
+          <t>-73,43; 35,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>57,27; 389,62</t>
+          <t>66,63; 383,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78,33; 454,85</t>
+          <t>91,57; 506,24</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9,76</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23,73</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>13,04</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>25,11</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,76</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,83</t>
+          <t>26,95</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23,36</t>
+          <t>25,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 7,61</t>
+          <t>-3,2; 10,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,27; 20,96</t>
+          <t>2,16; 17,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,7; 33,49</t>
+          <t>14,72; 33,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 10,89</t>
+          <t>-6,72; 7,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 17,32</t>
+          <t>5,76; 22,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,26; 31,86</t>
+          <t>18,25; 37,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 6,57</t>
+          <t>-2,94; 7,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,01; 17,24</t>
+          <t>6,15; 16,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,01; 29,88</t>
+          <t>19,37; 32,47</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>47,8%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>141,33%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>343,75%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>6,39%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>168,28%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>324,15%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>47,8%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>141,33%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>316,16%</t>
+          <t>347,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>318,24%</t>
+          <t>344,77%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-59,37; 183,8</t>
+          <t>-38,43; 272,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37,35; 474,95</t>
+          <t>7,11; 449,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>126,7; 706,51</t>
+          <t>127,78; 832,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-39,55; 267,42</t>
+          <t>-66,69; 151,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,64; 470,83</t>
+          <t>47,55; 542,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>129,12; 892,08</t>
+          <t>159,46; 911,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,62; 131,25</t>
+          <t>-31,92; 130,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>60,42; 333,2</t>
+          <t>55,53; 323,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>170,58; 614,15</t>
+          <t>189,05; 618,75</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,33</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>12,87</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>27,04</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,57</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>11,63</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>22,37</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>12,87</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,81</t>
+          <t>24,02</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23,69</t>
+          <t>25,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 1,27</t>
+          <t>-3,09; 2,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,72; 15,71</t>
+          <t>8,86; 16,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,62; 26,54</t>
+          <t>22,45; 32,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 2,53</t>
+          <t>-4,53; 1,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,09; 17,39</t>
+          <t>7,55; 15,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,09; 29,84</t>
+          <t>19,22; 28,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,07</t>
+          <t>-3,07; 1,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,73; 15,3</t>
+          <t>9,25; 14,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,52; 27,43</t>
+          <t>22,4; 29,03</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-4,97%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>192,91%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>405,14%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-21,42%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>158,58%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>304,99%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-4,97%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>192,91%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>371,71%</t>
+          <t>327,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>338,43%</t>
+          <t>366,09%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-52,23; 22,77</t>
+          <t>-39,01; 51,73</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>79,23; 258,15</t>
+          <t>109,15; 321,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>191,82; 456,57</t>
+          <t>257,44; 635,23</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-41,29; 49,25</t>
+          <t>-50,04; 28,52</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>109,37; 330,73</t>
+          <t>81,22; 271,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>235,84; 601,88</t>
+          <t>217,28; 526,78</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 17,56</t>
+          <t>-37,85; 20,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>115,9; 257,19</t>
+          <t>112,14; 258,28</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>253,06; 470,21</t>
+          <t>272,29; 503,43</t>
         </is>
       </c>
     </row>
